--- a/tame_output/ON/bt/strategyON_20240109.xlsx
+++ b/tame_output/ON/bt/strategyON_20240109.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
     </row>
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.6%</t>
+          <t>130.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-07</t>
+          <t>2024-01-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1836"/>
+  <dimension ref="A1:G1837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.310321938075317</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43789,6 +43789,29 @@
       </c>
       <c r="G1836" t="n">
         <v>4.458129948695317</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="2" t="n">
+        <v>45299</v>
+      </c>
+      <c r="B1837" t="n">
+        <v>3.383603738727791</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>3.118490189491276</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>1.619924881177275</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>3.766103717648439</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>2.233548163216526</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>4.458619087421192</v>
       </c>
     </row>
   </sheetData>
